--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/134.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/134.xlsx
@@ -426,13 +426,13 @@
         <v>-17.41626177676168</v>
       </c>
       <c r="E2">
-        <v>-14.05483212993176</v>
+        <v>-19.00496140940432</v>
       </c>
       <c r="F2">
-        <v>-1.520123085879033</v>
+        <v>-1.873378708068076</v>
       </c>
       <c r="G2">
-        <v>-9.220421786307014</v>
+        <v>-14.52633587450411</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.23949311827065</v>
       </c>
       <c r="E3">
-        <v>-14.38051998056341</v>
+        <v>-19.53548119635092</v>
       </c>
       <c r="F3">
-        <v>-1.488495190072745</v>
+        <v>-2.205212749220725</v>
       </c>
       <c r="G3">
-        <v>-9.088700428024666</v>
+        <v>-13.51595424153664</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.05416428938387</v>
       </c>
       <c r="E4">
-        <v>-14.58160234040001</v>
+        <v>-21.77408250882867</v>
       </c>
       <c r="F4">
-        <v>-1.915774551743355</v>
+        <v>-2.037520537300201</v>
       </c>
       <c r="G4">
-        <v>-8.311887629933928</v>
+        <v>-13.49352052973471</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.86133204182546</v>
       </c>
       <c r="E5">
-        <v>-16.27268850298038</v>
+        <v>-21.0289719240806</v>
       </c>
       <c r="F5">
-        <v>-1.423569409776125</v>
+        <v>-2.051328593537466</v>
       </c>
       <c r="G5">
-        <v>-9.190411733924334</v>
+        <v>-13.10947651475263</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.66749379380742</v>
       </c>
       <c r="E6">
-        <v>-16.88269206570961</v>
+        <v>-21.41813086640376</v>
       </c>
       <c r="F6">
-        <v>-1.651326542073641</v>
+        <v>-1.852058187854823</v>
       </c>
       <c r="G6">
-        <v>-8.53381961255009</v>
+        <v>-11.51548533094686</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.46978736341709</v>
       </c>
       <c r="E7">
-        <v>-16.81999987154742</v>
+        <v>-23.40145304212113</v>
       </c>
       <c r="F7">
-        <v>-1.07734662683685</v>
+        <v>-1.265226152363597</v>
       </c>
       <c r="G7">
-        <v>-8.445141318684536</v>
+        <v>-11.92040775871169</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.27807485253703</v>
       </c>
       <c r="E8">
-        <v>-18.17788544511741</v>
+        <v>-21.89592110200505</v>
       </c>
       <c r="F8">
-        <v>-1.179412259637985</v>
+        <v>-2.056369209183501</v>
       </c>
       <c r="G8">
-        <v>-7.087053558895047</v>
+        <v>-11.0657742288956</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.0920434096725</v>
       </c>
       <c r="E9">
-        <v>-18.2918807213125</v>
+        <v>-22.93113931710651</v>
       </c>
       <c r="F9">
-        <v>-0.5127222930472758</v>
+        <v>-1.212611568407384</v>
       </c>
       <c r="G9">
-        <v>-7.719909323508269</v>
+        <v>-10.6240529013416</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.90653373600907</v>
       </c>
       <c r="E10">
-        <v>-19.73297247629943</v>
+        <v>-23.53723480676711</v>
       </c>
       <c r="F10">
-        <v>-0.4739323326763833</v>
+        <v>-1.787693212289899</v>
       </c>
       <c r="G10">
-        <v>-7.175518573359236</v>
+        <v>-11.21513543428153</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.71111889209092</v>
       </c>
       <c r="E11">
-        <v>-21.17508766641209</v>
+        <v>-25.54521905193025</v>
       </c>
       <c r="F11">
-        <v>-0.5502879263968306</v>
+        <v>-1.006817769427694</v>
       </c>
       <c r="G11">
-        <v>-7.357514808375397</v>
+        <v>-11.00919940676766</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.50574182312923</v>
       </c>
       <c r="E12">
-        <v>-20.02697459429941</v>
+        <v>-27.64532604383142</v>
       </c>
       <c r="F12">
-        <v>-0.5258602000556759</v>
+        <v>-0.6861907108675203</v>
       </c>
       <c r="G12">
-        <v>-7.809808231793935</v>
+        <v>-9.438691925662837</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.28198226437373</v>
       </c>
       <c r="E13">
-        <v>-20.85210784323703</v>
+        <v>-25.63786710165318</v>
       </c>
       <c r="F13">
-        <v>-0.210757523704772</v>
+        <v>-0.210306891837649</v>
       </c>
       <c r="G13">
-        <v>-6.645479886311215</v>
+        <v>-9.055697901579771</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.04967346169957</v>
       </c>
       <c r="E14">
-        <v>-22.20115836401806</v>
+        <v>-27.81511664827502</v>
       </c>
       <c r="F14">
-        <v>-0.07451759370114287</v>
+        <v>-0.2884227662890452</v>
       </c>
       <c r="G14">
-        <v>-5.441173137348221</v>
+        <v>-9.94975202721103</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.81104643143634</v>
       </c>
       <c r="E15">
-        <v>-22.87524889090384</v>
+        <v>-27.81158896702304</v>
       </c>
       <c r="F15">
-        <v>0.1432767638429031</v>
+        <v>-0.4781868276571616</v>
       </c>
       <c r="G15">
-        <v>-5.282188109128446</v>
+        <v>-9.007099729062835</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.56814619522499</v>
       </c>
       <c r="E16">
-        <v>-23.8635340013898</v>
+        <v>-28.20501826033543</v>
       </c>
       <c r="F16">
-        <v>0.2789177842143082</v>
+        <v>-0.4160692128560322</v>
       </c>
       <c r="G16">
-        <v>-4.625179272616152</v>
+        <v>-9.896553582067753</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.32080737236832</v>
       </c>
       <c r="E17">
-        <v>-23.89971198023708</v>
+        <v>-30.05403721817031</v>
       </c>
       <c r="F17">
-        <v>0.6827294973636083</v>
+        <v>0.1789172713483519</v>
       </c>
       <c r="G17">
-        <v>-4.608674728172145</v>
+        <v>-8.228265698491478</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.07720925743407</v>
       </c>
       <c r="E18">
-        <v>-24.98471171010486</v>
+        <v>-30.20957218643776</v>
       </c>
       <c r="F18">
-        <v>1.05108128710127</v>
+        <v>0.6386106494905067</v>
       </c>
       <c r="G18">
-        <v>-4.380849671635221</v>
+        <v>-7.207618763875284</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.83683648999438</v>
       </c>
       <c r="E19">
-        <v>-25.92701469551694</v>
+        <v>-31.83028812717594</v>
       </c>
       <c r="F19">
-        <v>0.9435045259693096</v>
+        <v>0.1931428247566278</v>
       </c>
       <c r="G19">
-        <v>-3.960577689415303</v>
+        <v>-8.566208550563369</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.61011266201197</v>
       </c>
       <c r="E20">
-        <v>-27.02743840785484</v>
+        <v>-29.35919495914439</v>
       </c>
       <c r="F20">
-        <v>0.916246268212789</v>
+        <v>0.7101724810509532</v>
       </c>
       <c r="G20">
-        <v>-4.364459969945794</v>
+        <v>-6.145339690112854</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.39572037093148</v>
       </c>
       <c r="E21">
-        <v>-26.27913072045735</v>
+        <v>-31.65164435604735</v>
       </c>
       <c r="F21">
-        <v>1.066424308135923</v>
+        <v>1.064217537374865</v>
       </c>
       <c r="G21">
-        <v>-2.860456287407798</v>
+        <v>-6.859947089879641</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.18813425388235</v>
       </c>
       <c r="E22">
-        <v>-28.18001655533909</v>
+        <v>-31.2728239198837</v>
       </c>
       <c r="F22">
-        <v>1.502276444058105</v>
+        <v>0.2973978326033623</v>
       </c>
       <c r="G22">
-        <v>-2.306277653346942</v>
+        <v>-6.207171029179031</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.9798417121876</v>
       </c>
       <c r="E23">
-        <v>-28.08655790876879</v>
+        <v>-33.46561518929987</v>
       </c>
       <c r="F23">
-        <v>1.212773633923317</v>
+        <v>0.619339510231779</v>
       </c>
       <c r="G23">
-        <v>-2.517663789871049</v>
+        <v>-5.405230636386063</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.77147296561365</v>
       </c>
       <c r="E24">
-        <v>-27.41014427471707</v>
+        <v>-33.80013809272048</v>
       </c>
       <c r="F24">
-        <v>1.097305844912288</v>
+        <v>0.5788571952569672</v>
       </c>
       <c r="G24">
-        <v>-1.833260034558951</v>
+        <v>-4.873321653049159</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.56034018364077</v>
       </c>
       <c r="E25">
-        <v>-28.69604069698713</v>
+        <v>-34.04915208569126</v>
       </c>
       <c r="F25">
-        <v>1.84869140823483</v>
+        <v>0.3481386494944433</v>
       </c>
       <c r="G25">
-        <v>-2.12901950226262</v>
+        <v>-6.076424193699837</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.35658568512736</v>
       </c>
       <c r="E26">
-        <v>-28.10936330387141</v>
+        <v>-33.28453736339215</v>
       </c>
       <c r="F26">
-        <v>1.298246239278976</v>
+        <v>0.5245278907769588</v>
       </c>
       <c r="G26">
-        <v>-1.490880970938693</v>
+        <v>-4.691873382033426</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.16377247015576</v>
       </c>
       <c r="E27">
-        <v>-28.20928408285066</v>
+        <v>-31.39523762925905</v>
       </c>
       <c r="F27">
-        <v>1.717690073686505</v>
+        <v>0.5672666785569965</v>
       </c>
       <c r="G27">
-        <v>-1.876020913921635</v>
+        <v>-3.340994466010036</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.98370253889357</v>
       </c>
       <c r="E28">
-        <v>-28.58152917475517</v>
+        <v>-33.87156797748047</v>
       </c>
       <c r="F28">
-        <v>1.525807048502028</v>
+        <v>0.5820149317964389</v>
       </c>
       <c r="G28">
-        <v>-1.073220841080094</v>
+        <v>-4.822866309129577</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.81691012420473</v>
       </c>
       <c r="E29">
-        <v>-29.36057614371672</v>
+        <v>-34.34255644512223</v>
       </c>
       <c r="F29">
-        <v>1.448008438765904</v>
+        <v>0.5023674060172664</v>
       </c>
       <c r="G29">
-        <v>-1.223146416574242</v>
+        <v>-5.452306322099417</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.66858042465012</v>
       </c>
       <c r="E30">
-        <v>-28.37759840476775</v>
+        <v>-33.01085677250159</v>
       </c>
       <c r="F30">
-        <v>1.448513742881611</v>
+        <v>1.144118543579294</v>
       </c>
       <c r="G30">
-        <v>-1.830215060951787</v>
+        <v>-4.526427628563104</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.53928184924306</v>
       </c>
       <c r="E31">
-        <v>-28.96504563846477</v>
+        <v>-32.96497200961888</v>
       </c>
       <c r="F31">
-        <v>1.362434772587104</v>
+        <v>0.4799666947107622</v>
       </c>
       <c r="G31">
-        <v>-2.082298188477687</v>
+        <v>-5.561915528292667</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.43665320740305</v>
       </c>
       <c r="E32">
-        <v>-26.94881957060768</v>
+        <v>-31.26293146841395</v>
       </c>
       <c r="F32">
-        <v>1.233429803479525</v>
+        <v>0.9186899520510475</v>
       </c>
       <c r="G32">
-        <v>-2.706225749227658</v>
+        <v>-5.911316406050138</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.36020789786186</v>
       </c>
       <c r="E33">
-        <v>-27.82910510448471</v>
+        <v>-33.17453393703483</v>
       </c>
       <c r="F33">
-        <v>1.189488226230623</v>
+        <v>0.5756472715711191</v>
       </c>
       <c r="G33">
-        <v>-2.936869375084147</v>
+        <v>-6.458046667171055</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.30514028277529</v>
       </c>
       <c r="E34">
-        <v>-28.89772081539274</v>
+        <v>-31.55899404208742</v>
       </c>
       <c r="F34">
-        <v>1.308968626940812</v>
+        <v>0.5281768491862906</v>
       </c>
       <c r="G34">
-        <v>-2.251747032250531</v>
+        <v>-6.005300435177313</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.26488843526874</v>
       </c>
       <c r="E35">
-        <v>-27.16835999049954</v>
+        <v>-31.5782876055971</v>
       </c>
       <c r="F35">
-        <v>0.8970082636501733</v>
+        <v>0.1744946177848053</v>
       </c>
       <c r="G35">
-        <v>-3.004902222897673</v>
+        <v>-4.529744943559702</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.23620696903823</v>
       </c>
       <c r="E36">
-        <v>-26.10987900442067</v>
+        <v>-28.91009260638169</v>
       </c>
       <c r="F36">
-        <v>0.9238920993406284</v>
+        <v>0.5354813929441766</v>
       </c>
       <c r="G36">
-        <v>-3.127498504023206</v>
+        <v>-7.28593824127767</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.21355289827321</v>
       </c>
       <c r="E37">
-        <v>-26.21956770183446</v>
+        <v>-30.68075990693586</v>
       </c>
       <c r="F37">
-        <v>1.499607444286285</v>
+        <v>0.5771689824900618</v>
       </c>
       <c r="G37">
-        <v>-3.017656331099235</v>
+        <v>-7.032841216289901</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.19843018641811</v>
       </c>
       <c r="E38">
-        <v>-25.7781003562487</v>
+        <v>-28.94636568318313</v>
       </c>
       <c r="F38">
-        <v>1.081745791618102</v>
+        <v>0.7378043325061363</v>
       </c>
       <c r="G38">
-        <v>-3.678819194105786</v>
+        <v>-6.142954242039138</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.18776548938184</v>
       </c>
       <c r="E39">
-        <v>-25.73539684635637</v>
+        <v>-27.10828525431378</v>
       </c>
       <c r="F39">
-        <v>0.7982403614795827</v>
+        <v>0.07024623687729312</v>
       </c>
       <c r="G39">
-        <v>-4.716384107082478</v>
+        <v>-7.396882904645614</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.17660142712179</v>
       </c>
       <c r="E40">
-        <v>-24.05468541772757</v>
+        <v>-29.06534680926066</v>
       </c>
       <c r="F40">
-        <v>0.8652171794655339</v>
+        <v>0.5861642241170616</v>
       </c>
       <c r="G40">
-        <v>-3.516064042314209</v>
+        <v>-6.781922922417604</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.16262702948809</v>
       </c>
       <c r="E41">
-        <v>-22.78621456343903</v>
+        <v>-27.04620440414263</v>
       </c>
       <c r="F41">
-        <v>1.405084096687639</v>
+        <v>0.1915788671001423</v>
       </c>
       <c r="G41">
-        <v>-4.459411959433005</v>
+        <v>-6.765861342884123</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.14850679828666</v>
       </c>
       <c r="E42">
-        <v>-23.14297680271132</v>
+        <v>-26.70551371912356</v>
       </c>
       <c r="F42">
-        <v>1.291702136796859</v>
+        <v>0.8810257429805597</v>
       </c>
       <c r="G42">
-        <v>-3.677893889626022</v>
+        <v>-6.963259631900317</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.13706429235613</v>
       </c>
       <c r="E43">
-        <v>-22.17960282774155</v>
+        <v>-27.72425734578512</v>
       </c>
       <c r="F43">
-        <v>1.333209970616337</v>
+        <v>0.7465386384012543</v>
       </c>
       <c r="G43">
-        <v>-3.998836732798429</v>
+        <v>-7.742759750448241</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.13680313155165</v>
       </c>
       <c r="E44">
-        <v>-21.27824630430683</v>
+        <v>-27.52602792457336</v>
       </c>
       <c r="F44">
-        <v>1.126818918739229</v>
+        <v>0.6416507578587809</v>
       </c>
       <c r="G44">
-        <v>-3.645980728738863</v>
+        <v>-7.214469954491404</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.15185814232813</v>
       </c>
       <c r="E45">
-        <v>-21.42026830613538</v>
+        <v>-26.71875497712199</v>
       </c>
       <c r="F45">
-        <v>0.9896876654101876</v>
+        <v>0.9808108803217881</v>
       </c>
       <c r="G45">
-        <v>-3.692511731673349</v>
+        <v>-8.458371204012218</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.18206164037432</v>
       </c>
       <c r="E46">
-        <v>-19.47831826895209</v>
+        <v>-26.24374975303542</v>
       </c>
       <c r="F46">
-        <v>0.9322884313354043</v>
+        <v>0.2314780114233833</v>
       </c>
       <c r="G46">
-        <v>-4.320311133863465</v>
+        <v>-6.824795363313309</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.22843136313775</v>
       </c>
       <c r="E47">
-        <v>-18.98300736741513</v>
+        <v>-24.69927293645338</v>
       </c>
       <c r="F47">
-        <v>1.627209159013521</v>
+        <v>0.2944571283234241</v>
       </c>
       <c r="G47">
-        <v>-5.265601534145453</v>
+        <v>-8.770346468662662</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.29371845225509</v>
       </c>
       <c r="E48">
-        <v>-19.28966657026655</v>
+        <v>-24.8196080762592</v>
       </c>
       <c r="F48">
-        <v>1.266928981248737</v>
+        <v>0.5814408731862988</v>
       </c>
       <c r="G48">
-        <v>-4.4354557608275</v>
+        <v>-8.668339852822644</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.37886793317079</v>
       </c>
       <c r="E49">
-        <v>-16.83521554421319</v>
+        <v>-24.69377084053406</v>
       </c>
       <c r="F49">
-        <v>1.496723068989737</v>
+        <v>0.6632852293176956</v>
       </c>
       <c r="G49">
-        <v>-5.139067787148586</v>
+        <v>-8.562339990344784</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.48728194728454</v>
       </c>
       <c r="E50">
-        <v>-16.38609960602848</v>
+        <v>-23.11413948023047</v>
       </c>
       <c r="F50">
-        <v>1.60097476336686</v>
+        <v>0.8768275769831717</v>
       </c>
       <c r="G50">
-        <v>-3.979306902076614</v>
+        <v>-8.303372859987167</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.6164177255214</v>
       </c>
       <c r="E51">
-        <v>-16.29105146508148</v>
+        <v>-20.65542716013589</v>
       </c>
       <c r="F51">
-        <v>1.343264694151517</v>
+        <v>0.7695639387294694</v>
       </c>
       <c r="G51">
-        <v>-4.997276359900302</v>
+        <v>-9.137118133355832</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.75810589750004</v>
       </c>
       <c r="E52">
-        <v>-15.59042860898476</v>
+        <v>-22.60027542068408</v>
       </c>
       <c r="F52">
-        <v>1.544748497534441</v>
+        <v>0.9685957746001066</v>
       </c>
       <c r="G52">
-        <v>-4.346882466051849</v>
+        <v>-9.088628241150358</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.90667631646239</v>
       </c>
       <c r="E53">
-        <v>-15.71885613184229</v>
+        <v>-19.86414425440561</v>
       </c>
       <c r="F53">
-        <v>1.488293602298849</v>
+        <v>0.6649179414686134</v>
       </c>
       <c r="G53">
-        <v>-5.236638191440234</v>
+        <v>-10.14629719862177</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.05794826804394</v>
       </c>
       <c r="E54">
-        <v>-14.41639908012618</v>
+        <v>-20.23574630300103</v>
       </c>
       <c r="F54">
-        <v>1.355501337425672</v>
+        <v>0.7481622385107414</v>
       </c>
       <c r="G54">
-        <v>-4.68782763585063</v>
+        <v>-7.963093778164954</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.20841619101575</v>
       </c>
       <c r="E55">
-        <v>-14.08015988505666</v>
+        <v>-19.94554810316749</v>
       </c>
       <c r="F55">
-        <v>1.248178056718968</v>
+        <v>0.3991644247720872</v>
       </c>
       <c r="G55">
-        <v>-5.044178140871005</v>
+        <v>-8.855704166310057</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.35788594791775</v>
       </c>
       <c r="E56">
-        <v>-13.82095908980562</v>
+        <v>-20.05804445446604</v>
       </c>
       <c r="F56">
-        <v>1.206188113071061</v>
+        <v>0.7877350060772793</v>
       </c>
       <c r="G56">
-        <v>-4.891240403985287</v>
+        <v>-9.336550779738882</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.50247212680327</v>
       </c>
       <c r="E57">
-        <v>-13.83652345496999</v>
+        <v>-18.69415412436187</v>
       </c>
       <c r="F57">
-        <v>1.294157417778757</v>
+        <v>0.4965804313413091</v>
       </c>
       <c r="G57">
-        <v>-5.696501392996411</v>
+        <v>-8.955413927058462</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.63356115231002</v>
       </c>
       <c r="E58">
-        <v>-13.54369421173799</v>
+        <v>-18.01891336507815</v>
       </c>
       <c r="F58">
-        <v>1.149657008034411</v>
+        <v>1.032098419698717</v>
       </c>
       <c r="G58">
-        <v>-4.963286185766014</v>
+        <v>-9.321496535224149</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.74738074221997</v>
       </c>
       <c r="E59">
-        <v>-12.24198435823315</v>
+        <v>-18.94715543869641</v>
       </c>
       <c r="F59">
-        <v>0.9067051324673443</v>
+        <v>0.6178103440062112</v>
       </c>
       <c r="G59">
-        <v>-5.239305824568063</v>
+        <v>-10.02724135555888</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.84030858614833</v>
       </c>
       <c r="E60">
-        <v>-12.28279949446428</v>
+        <v>-17.4127363628854</v>
       </c>
       <c r="F60">
-        <v>0.9090842036481845</v>
+        <v>0.3617669500053007</v>
       </c>
       <c r="G60">
-        <v>-6.355810365821876</v>
+        <v>-10.31481745669329</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.91120915003372</v>
       </c>
       <c r="E61">
-        <v>-11.27960664754507</v>
+        <v>-20.78141383550329</v>
       </c>
       <c r="F61">
-        <v>0.4576513052467463</v>
+        <v>0.6371618349030104</v>
       </c>
       <c r="G61">
-        <v>-6.65543183130101</v>
+        <v>-9.901166979580331</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.96171961455054</v>
       </c>
       <c r="E62">
-        <v>-11.44964631805908</v>
+        <v>-18.45809835976404</v>
       </c>
       <c r="F62">
-        <v>0.4446318547769465</v>
+        <v>0.7043573418833007</v>
       </c>
       <c r="G62">
-        <v>-6.758698436219855</v>
+        <v>-9.807353573974249</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.99073849313851</v>
       </c>
       <c r="E63">
-        <v>-12.32009147791745</v>
+        <v>-19.1371973789023</v>
       </c>
       <c r="F63">
-        <v>0.601469968618588</v>
+        <v>-0.759519450098138</v>
       </c>
       <c r="G63">
-        <v>-5.895212170636383</v>
+        <v>-9.90856613419688</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.99311572643046</v>
       </c>
       <c r="E64">
-        <v>-11.4415086502673</v>
+        <v>-18.85131028632406</v>
       </c>
       <c r="F64">
-        <v>0.7188512863300837</v>
+        <v>-0.5890480655412222</v>
       </c>
       <c r="G64">
-        <v>-7.460459853581415</v>
+        <v>-9.972031521599659</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.96970123387619</v>
       </c>
       <c r="E65">
-        <v>-10.18809950052827</v>
+        <v>-16.22437421379254</v>
       </c>
       <c r="F65">
-        <v>0.3899943976230967</v>
+        <v>-0.3241792452308859</v>
       </c>
       <c r="G65">
-        <v>-6.693956653630451</v>
+        <v>-11.20971485626533</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.92056429366607</v>
       </c>
       <c r="E66">
-        <v>-11.60431181931705</v>
+        <v>-18.19058328623492</v>
       </c>
       <c r="F66">
-        <v>0.4094883677131775</v>
+        <v>-0.5313887241019598</v>
       </c>
       <c r="G66">
-        <v>-6.57714188489266</v>
+        <v>-11.58162163269903</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.84999923223982</v>
       </c>
       <c r="E67">
-        <v>-11.01701402526229</v>
+        <v>-17.51089556547566</v>
       </c>
       <c r="F67">
-        <v>-0.0003927933964347178</v>
+        <v>-0.4748692162089496</v>
       </c>
       <c r="G67">
-        <v>-6.606046165609809</v>
+        <v>-10.83619043760282</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.76361237912008</v>
       </c>
       <c r="E68">
-        <v>-10.79735586504623</v>
+        <v>-17.30842749259272</v>
       </c>
       <c r="F68">
-        <v>0.03731034894198478</v>
+        <v>-0.1834164292079715</v>
       </c>
       <c r="G68">
-        <v>-7.016792761642657</v>
+        <v>-11.06950497780869</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.66388057560202</v>
       </c>
       <c r="E69">
-        <v>-10.30084038942323</v>
+        <v>-17.56522819661969</v>
       </c>
       <c r="F69">
-        <v>0.5240151313546259</v>
+        <v>-0.3994927527586113</v>
       </c>
       <c r="G69">
-        <v>-5.845665725088768</v>
+        <v>-9.935728086265962</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.54820034225594</v>
       </c>
       <c r="E70">
-        <v>-9.457670228513059</v>
+        <v>-16.5432738818867</v>
       </c>
       <c r="F70">
-        <v>0.3367071793358101</v>
+        <v>-0.3897983690436487</v>
       </c>
       <c r="G70">
-        <v>-6.716429740091088</v>
+        <v>-9.21382981219409</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.42047491953247</v>
       </c>
       <c r="E71">
-        <v>-10.90623849408665</v>
+        <v>-16.39741173409964</v>
       </c>
       <c r="F71">
-        <v>0.03126823710596519</v>
+        <v>-0.3924400326911763</v>
       </c>
       <c r="G71">
-        <v>-7.186038169678816</v>
+        <v>-10.24090137862368</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.28169743640598</v>
       </c>
       <c r="E72">
-        <v>-10.75851061500843</v>
+        <v>-17.14856783164795</v>
       </c>
       <c r="F72">
-        <v>-0.05435595948440571</v>
+        <v>-0.3357871576463153</v>
       </c>
       <c r="G72">
-        <v>-6.450283296961408</v>
+        <v>-9.703909783091193</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.13791692639663</v>
       </c>
       <c r="E73">
-        <v>-12.5401028591061</v>
+        <v>-17.74850459665813</v>
       </c>
       <c r="F73">
-        <v>0.4634391082901065</v>
+        <v>-0.662426506816008</v>
       </c>
       <c r="G73">
-        <v>-5.587991396025575</v>
+        <v>-10.27362828245758</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.99455109072173</v>
       </c>
       <c r="E74">
-        <v>-10.54686785378595</v>
+        <v>-18.87538365414884</v>
       </c>
       <c r="F74">
-        <v>-0.3004084142401512</v>
+        <v>-1.07171290013041</v>
       </c>
       <c r="G74">
-        <v>-6.401484969929347</v>
+        <v>-10.51939177725999</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.85363094699628</v>
       </c>
       <c r="E75">
-        <v>-11.90967587860228</v>
+        <v>-18.11770202555547</v>
       </c>
       <c r="F75">
-        <v>-0.185240494228936</v>
+        <v>-0.1222033916106992</v>
       </c>
       <c r="G75">
-        <v>-6.30438049909914</v>
+        <v>-9.227824222145122</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.71215108286935</v>
       </c>
       <c r="E76">
-        <v>-11.76345145289461</v>
+        <v>-18.80068647539232</v>
       </c>
       <c r="F76">
-        <v>0.07748285450814961</v>
+        <v>-0.6715542872274558</v>
       </c>
       <c r="G76">
-        <v>-6.179185490498527</v>
+        <v>-7.891113620815415</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.57335968534303</v>
       </c>
       <c r="E77">
-        <v>-11.98886077510041</v>
+        <v>-20.10709235644312</v>
       </c>
       <c r="F77">
-        <v>0.3704399567126115</v>
+        <v>-0.6612568520432551</v>
       </c>
       <c r="G77">
-        <v>-4.743608402361191</v>
+        <v>-9.938490874819015</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.43627251755715</v>
       </c>
       <c r="E78">
-        <v>-13.00471070687106</v>
+        <v>-17.73445727028633</v>
       </c>
       <c r="F78">
-        <v>-0.4007883193765898</v>
+        <v>-0.970488888610519</v>
       </c>
       <c r="G78">
-        <v>-5.299864049669175</v>
+        <v>-10.04075342594067</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.30589637457609</v>
       </c>
       <c r="E79">
-        <v>-13.98508457326562</v>
+        <v>-21.02876361427625</v>
       </c>
       <c r="F79">
-        <v>-0.3007778661017999</v>
+        <v>-1.154161964465851</v>
       </c>
       <c r="G79">
-        <v>-4.651583262505004</v>
+        <v>-8.967931787307744</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.18535846734805</v>
       </c>
       <c r="E80">
-        <v>-14.02453211034644</v>
+        <v>-20.21108423355526</v>
       </c>
       <c r="F80">
-        <v>-0.2080628445434652</v>
+        <v>-1.312513505552407</v>
       </c>
       <c r="G80">
-        <v>-4.43107533004564</v>
+        <v>-9.961167397016338</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.07430645772642</v>
       </c>
       <c r="E81">
-        <v>-15.19276066400119</v>
+        <v>-21.4833318351662</v>
       </c>
       <c r="F81">
-        <v>-0.2233636188405748</v>
+        <v>-0.5601446701227418</v>
       </c>
       <c r="G81">
-        <v>-3.846870237494306</v>
+        <v>-8.988557546030414</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.96634069135335</v>
       </c>
       <c r="E82">
-        <v>-15.89150420338473</v>
+        <v>-21.75400325507866</v>
       </c>
       <c r="F82">
-        <v>0.2214638778909401</v>
+        <v>-0.9548037518385103</v>
       </c>
       <c r="G82">
-        <v>-3.549401253358167</v>
+        <v>-9.502367311245422</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.86146422061543</v>
       </c>
       <c r="E83">
-        <v>-16.94645297973761</v>
+        <v>-24.69954464489384</v>
       </c>
       <c r="F83">
-        <v>0.1620144344942279</v>
+        <v>-0.8478449527890382</v>
       </c>
       <c r="G83">
-        <v>-3.587515922992677</v>
+        <v>-8.087963945831182</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.75449654744189</v>
       </c>
       <c r="E84">
-        <v>-17.11930936108439</v>
+        <v>-22.60979880152222</v>
       </c>
       <c r="F84">
-        <v>0.3608723132102773</v>
+        <v>-0.7348531539449772</v>
       </c>
       <c r="G84">
-        <v>-2.672881975740582</v>
+        <v>-7.251324635047087</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.64696992315657</v>
       </c>
       <c r="E85">
-        <v>-19.59890700330235</v>
+        <v>-25.41857574783174</v>
       </c>
       <c r="F85">
-        <v>-0.1625059508591036</v>
+        <v>-0.6054282025641796</v>
       </c>
       <c r="G85">
-        <v>-3.01195356802892</v>
+        <v>-5.650085232816506</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.53790959929972</v>
       </c>
       <c r="E86">
-        <v>-19.65666316079618</v>
+        <v>-25.38525976455731</v>
       </c>
       <c r="F86">
-        <v>0.1222975309996029</v>
+        <v>-0.7394953248702656</v>
       </c>
       <c r="G86">
-        <v>-2.84372205745463</v>
+        <v>-5.3748793369612</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.42433155336627</v>
       </c>
       <c r="E87">
-        <v>-20.89968399116161</v>
+        <v>-26.57354945806604</v>
       </c>
       <c r="F87">
-        <v>0.04020714974957465</v>
+        <v>-0.7718306464385443</v>
       </c>
       <c r="G87">
-        <v>-3.07311225667541</v>
+        <v>-6.69615179085372</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.29895991104858</v>
       </c>
       <c r="E88">
-        <v>-22.99466475048611</v>
+        <v>-27.0932416636603</v>
       </c>
       <c r="F88">
-        <v>0.24509719989281</v>
+        <v>-0.3725459611455434</v>
       </c>
       <c r="G88">
-        <v>-3.076025981420197</v>
+        <v>-6.651235148926481</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.16226783125335</v>
       </c>
       <c r="E89">
-        <v>-24.19956941512898</v>
+        <v>-27.66720763023649</v>
       </c>
       <c r="F89">
-        <v>-0.1739548167331955</v>
+        <v>-0.5040791075664657</v>
       </c>
       <c r="G89">
-        <v>-2.326365291733863</v>
+        <v>-5.435460530613228</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.00992798276861</v>
       </c>
       <c r="E90">
-        <v>-25.95105183554965</v>
+        <v>-31.52182432743246</v>
       </c>
       <c r="F90">
-        <v>-0.01611106486455534</v>
+        <v>-0.9953954113104917</v>
       </c>
       <c r="G90">
-        <v>-2.227958175944556</v>
+        <v>-6.233187834923868</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.845607152601941</v>
       </c>
       <c r="E91">
-        <v>-27.8462227362337</v>
+        <v>-31.67767176040644</v>
       </c>
       <c r="F91">
-        <v>0.4348422088106619</v>
+        <v>-0.9398252124610896</v>
       </c>
       <c r="G91">
-        <v>-1.569633569586925</v>
+        <v>-4.772115655269646</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.670235327325644</v>
       </c>
       <c r="E92">
-        <v>-30.02882946760662</v>
+        <v>-34.17340435551372</v>
       </c>
       <c r="F92">
-        <v>0.1200385730921686</v>
+        <v>-0.7069645085949262</v>
       </c>
       <c r="G92">
-        <v>-1.632938177133292</v>
+        <v>-5.215080565794683</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.483486276717729</v>
       </c>
       <c r="E93">
-        <v>-31.62424255982694</v>
+        <v>-33.9769093398469</v>
       </c>
       <c r="F93">
-        <v>0.4564195229187835</v>
+        <v>-0.2898193937301652</v>
       </c>
       <c r="G93">
-        <v>-1.901010697318366</v>
+        <v>-6.520084723195476</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.281150386295671</v>
       </c>
       <c r="E94">
-        <v>-32.70095518226068</v>
+        <v>-36.56753837202192</v>
       </c>
       <c r="F94">
-        <v>-0.005690202937337557</v>
+        <v>-0.6403082687938584</v>
       </c>
       <c r="G94">
-        <v>-2.010915213451967</v>
+        <v>-6.315887743108112</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.066857938928674</v>
       </c>
       <c r="E95">
-        <v>-33.60666583345377</v>
+        <v>-38.87054817031078</v>
       </c>
       <c r="F95">
-        <v>-0.2163506604084742</v>
+        <v>-1.312935144560432</v>
       </c>
       <c r="G95">
-        <v>-3.212718390365104</v>
+        <v>-6.560089376448226</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.838256493211468</v>
       </c>
       <c r="E96">
-        <v>-36.23390757798082</v>
+        <v>-39.64354509799808</v>
       </c>
       <c r="F96">
-        <v>-0.5931037523453285</v>
+        <v>-0.6690832672649049</v>
       </c>
       <c r="G96">
-        <v>-2.435675906765204</v>
+        <v>-5.668883351130566</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.603324575779899</v>
       </c>
       <c r="E97">
-        <v>-39.21319968457516</v>
+        <v>-43.95157299097504</v>
       </c>
       <c r="F97">
-        <v>-0.2589428271582164</v>
+        <v>-0.8046480778352523</v>
       </c>
       <c r="G97">
-        <v>-2.99244998707958</v>
+        <v>-6.172862576553476</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.36472800136236</v>
       </c>
       <c r="E98">
-        <v>-39.70535650396578</v>
+        <v>-43.90603918482792</v>
       </c>
       <c r="F98">
-        <v>0.001012946086116043</v>
+        <v>-1.278895871244595</v>
       </c>
       <c r="G98">
-        <v>-2.547224314900086</v>
+        <v>-5.043400491361417</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.12815637295596</v>
       </c>
       <c r="E99">
-        <v>-42.70258816034151</v>
+        <v>-46.00482839079287</v>
       </c>
       <c r="F99">
-        <v>-0.7825298398131028</v>
+        <v>-2.34350206017888</v>
       </c>
       <c r="G99">
-        <v>-3.881490406168008</v>
+        <v>-5.686191794856637</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.89027661506537</v>
       </c>
       <c r="E100">
-        <v>-45.0444069808761</v>
+        <v>-50.12930364681692</v>
       </c>
       <c r="F100">
-        <v>-0.7372976661506385</v>
+        <v>-1.208329737302313</v>
       </c>
       <c r="G100">
-        <v>-3.727112213017693</v>
+        <v>-6.862414568492343</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.663625016450899</v>
       </c>
       <c r="E101">
-        <v>-46.85971144972387</v>
+        <v>-50.60722520816443</v>
       </c>
       <c r="F101">
-        <v>-0.8311193865591133</v>
+        <v>-1.509016335742297</v>
       </c>
       <c r="G101">
-        <v>-3.982611092186975</v>
+        <v>-6.877606624312572</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.43977468896194</v>
       </c>
       <c r="E102">
-        <v>-49.46270774441384</v>
+        <v>-52.93395854966096</v>
       </c>
       <c r="F102">
-        <v>-0.8688076182842824</v>
+        <v>-1.819633402607042</v>
       </c>
       <c r="G102">
-        <v>-4.19571987002979</v>
+        <v>-6.79300360762385</v>
       </c>
     </row>
   </sheetData>
